--- a/questions_answers.xlsx
+++ b/questions_answers.xlsx
@@ -1,15 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\chataddb\stubot\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF18A18D-C3AD-4F6F-946D-2E7E11F0DC30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$42</definedName>
+  </definedNames>
+  <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -166,12 +180,6 @@
     <t>Anudip evaluates training effectiveness during the course through participant feedback, observation, interactive activities, and ongoing assessments like quizzes and skill demonstrations. This helps trainers adjust content and methods in real-time to ensure learning objectives are being met.</t>
   </si>
   <si>
-    <t>Please contact the faculty for guidance</t>
-  </si>
-  <si>
-    <t>All our learning content is available on Learning Management System</t>
-  </si>
-  <si>
     <t>There is a minimum requirement of 60% or above attendance for certification &amp; placement.</t>
   </si>
   <si>
@@ -208,12 +216,6 @@
     <t>If you lose your certificate then you can reapply for the duplicate certificate with the help of your trainer.</t>
   </si>
   <si>
-    <t>Obviously, as we provide livelihood to the students so that we have the responsibility to support you with the Placement opportunities.</t>
-  </si>
-  <si>
-    <t>As you know if you do not appear for the final assessment test then you will not be able to get the certificate. So that it will be better to take the final assessment at first &amp; after that you will get the placement opportunities. Additionally in an immediate basis you can join the job but you need to take the final assessment as per trainer's insturction.</t>
-  </si>
-  <si>
     <t>Absolutely not. There is no need to pay anything for placement support.</t>
   </si>
   <si>
@@ -262,17 +264,29 @@
     <t>All placed candidates are encouraged to join Anudip Alumni Network in social media. Please reach out to your faculty for guidance</t>
   </si>
   <si>
-    <t>If your concern is not listed please contact your faculty for any concern/support/guidance</t>
-  </si>
-  <si>
-    <t>Yes, you can get the email ID &amp; contact number of Anudip through Anudip's official website anudip.org</t>
+    <t xml:space="preserve">If you experience technical difficulties during an online class, follow these immediate steps to reconnect: 1. Quick Fixes: Check your internet connection, refresh your browser or app, or restart your device. 2. Notify Your Trainer: Inform your Batch Trainer or Class Coordinator via WhatsApp or phone call so they are aware of your absence/delay. </t>
+  </si>
+  <si>
+    <t>If your question or issue is not listed here, our support team is ready to help you directly. You can reach out through any of the following support channels: 1. Submit a Query: Log into the Anudip Care Portal and click on "Raise a Ticket" to submit your specific concern. 2. Contact Your Center: Reach out directly to your assigned Center Coordinator or Batch Trainer. 3. Email Support: Write to us at info@anudip.org with your Student ID, full name, and batch details for a swift resolution. 4.Helpline: Call our student support helpline at 1800-120-5300 during working hours (Monday to Friday, 9:30 AM – 6:00 PM). Our support team typically responds to portal tickets and emails within 24–48 working hours.</t>
+  </si>
+  <si>
+    <t>Yes! Upon successful admission, students receive a digital student kit along with access to Anudip's learning resources. Depending on your course and center type, your onboarding kit includes: 1.Digital Learning Kit: Access to the Anudip LMS (Learning Management System), which includes self-study content, video tutorials, practice assignments, and software tools required for your course. 2. Course Study Material: E-modules and reference study guides for both technical domain modules and soft skills/communicative English. 3. Student Identity &amp; Credentials: Anudip Student ID/Registration details and login credentials to access online portals, mock tests, and batch updates. Please check with your batch trainer after your orientation to get access to the learning resources.</t>
+  </si>
+  <si>
+    <t>Contact Information - General Enquiries / Support Email: info@anudip.org Contact Numbers:033 4062 4187 / 033 4060 8484 / 8145111444 Refer to the link for more details: https://anudip.org/contact-us/</t>
+  </si>
+  <si>
+    <t>The students should need to complete 50-60% of the module to be eligble for the Placement. Anything less than the specified %, would not be able to sit for the placement drives. Secondly, students into NON_LIVELIHOOD projects are the exceptions, where placement is not provided.</t>
+  </si>
+  <si>
+    <t>As per the Company's norm, a student needs to complete the Final Assessment or the END TEST and also needs to Clear the Assessment to get the Placement Support from the CRD.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -324,10 +338,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -335,6 +352,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -381,7 +406,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -413,9 +438,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -447,6 +490,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -622,11 +683,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.7265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="2" customWidth="1"/>
+    <col min="3" max="16384" width="8.7265625" style="2"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -637,335 +703,336 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:3" ht="362.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
+    <row r="4" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
+    <row r="5" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
+    <row r="6" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
+    <row r="7" spans="1:3" ht="145" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
+    <row r="8" spans="1:3" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="348" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
+    <row r="11" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
+    <row r="12" spans="1:3" ht="116" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
+    <row r="13" spans="1:3" ht="87" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
+    <row r="14" spans="1:3" ht="87" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
+    <row r="16" spans="1:3" ht="87" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" t="s">
+    <row r="17" spans="1:2" ht="116" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" t="s">
+    <row r="18" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" t="s">
+    <row r="19" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" t="s">
+    <row r="20" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" t="s">
+    <row r="21" spans="1:2" ht="116" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" t="s">
+    <row r="22" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" t="s">
+    <row r="23" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="87" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
-      <c r="A22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" t="s">
+    <row r="26" spans="1:2" ht="145" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
-      <c r="A23" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" t="s">
+    <row r="27" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
-      <c r="A24" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" t="s">
+    <row r="28" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
-      <c r="A25" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" t="s">
+    <row r="29" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
-      <c r="A26" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" t="s">
+    <row r="30" spans="1:2" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
-      <c r="A27" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" t="s">
+    <row r="31" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
-      <c r="A28" t="s">
-        <v>29</v>
-      </c>
-      <c r="B28" t="s">
+    <row r="32" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
-      <c r="A29" t="s">
-        <v>30</v>
-      </c>
-      <c r="B29" t="s">
+    <row r="33" spans="1:2" ht="116" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
-      <c r="A30" t="s">
-        <v>31</v>
-      </c>
-      <c r="B30" t="s">
+    <row r="34" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
-      <c r="A31" t="s">
-        <v>32</v>
-      </c>
-      <c r="B31" t="s">
+    <row r="35" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
-      <c r="A32" t="s">
-        <v>33</v>
-      </c>
-      <c r="B32" t="s">
+    <row r="36" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
-      <c r="A33" t="s">
-        <v>34</v>
-      </c>
-      <c r="B33" t="s">
+    <row r="37" spans="1:2" ht="116" x14ac:dyDescent="0.35">
+      <c r="A37" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
-      <c r="A34" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" t="s">
+    <row r="38" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="A38" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
-      <c r="A35" t="s">
-        <v>36</v>
-      </c>
-      <c r="B35" t="s">
+    <row r="39" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="A39" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
-      <c r="A36" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" t="s">
+    <row r="40" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
-      <c r="A37" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" t="s">
+    <row r="41" spans="1:2" ht="333.5" x14ac:dyDescent="0.35">
+      <c r="A41" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
-      <c r="A39" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" t="s">
+    <row r="42" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
-      <c r="A41" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" t="s">
-        <v>83</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:C42" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>